--- a/data/trans_orig/IP31B_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5911</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12141</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7741</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13572</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>5090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21938</t>
+          <t>24002</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13606</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26610</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>20589</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12021</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29656</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>38,93%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>56,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20932</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27904</t>
+          <t>21929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>41521</t>
+          <t>36290</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31022</t>
+          <t>28036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52353</t>
+          <t>45510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16719</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11469</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22990</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>32,95%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>45,31%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13299</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7732</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20417</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12760</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23540</t>
+          <t>23237</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41119</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6208</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12599</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>9047</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2340</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25300</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>47,84%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>1652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16049</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5617</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50740</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50740</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50740</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>52883</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>52883</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>52883</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108154</t>
+          <t>95955</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108154</t>
+          <t>95955</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108154</t>
+          <t>95955</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70428</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>56837</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>84804</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>76615</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>60519</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>92867</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,02%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>71895</t>
+          <t>80018</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>66303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87287</t>
+          <t>95650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>148509</t>
+          <t>150446</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128075</t>
+          <t>129602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171121</t>
+          <t>171492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>242183</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>222405</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>265642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>52,02%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>220809</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>177420</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>243382</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>49,05%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,06%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>254510</t>
+          <t>220558</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230762</t>
+          <t>203316</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>279615</t>
+          <t>238077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>475319</t>
+          <t>462740</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>433130</t>
+          <t>433756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>505665</t>
+          <t>492130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>110701</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>92582</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>131477</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>23,78%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>19,89%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28,24%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>126044</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>100622</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>195163</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>28,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>22,35%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>43,35%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>127453</t>
+          <t>98466</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107900</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152511</t>
+          <t>114823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>253497</t>
+          <t>209167</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222921</t>
+          <t>184651</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>323326</t>
+          <t>234981</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27445</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>19796</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36110</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11512</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6514</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17645</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31769</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23454</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42381</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>43282</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32861</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53960</t>
+          <t>48934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14807</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9577</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22963</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>15234</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9219</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21838</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25690</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>28282</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>21036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43988</t>
+          <t>37742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>465563</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>465563</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>465563</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>621</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>450214</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>450214</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>450214</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>503143</t>
+          <t>423272</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>503143</t>
+          <t>423272</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>503143</t>
+          <t>423272</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>953357</t>
+          <t>888834</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>953357</t>
+          <t>888834</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>953357</t>
+          <t>888834</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36328</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27656</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46416</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>27,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>36223</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28177</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45498</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>25,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>31,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>36839</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27986</t>
+          <t>29062</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48542</t>
+          <t>46175</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>72999</t>
+          <t>73167</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61093</t>
+          <t>60821</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87602</t>
+          <t>85836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>82425</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>71696</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>93270</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>43,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>55,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>66078</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>56839</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>76653</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>45,67%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>52,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>89678</t>
+          <t>67166</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77015</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102147</t>
+          <t>77159</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>155755</t>
+          <t>149591</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140322</t>
+          <t>135053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>172308</t>
+          <t>165589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39177</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31465</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>51142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>23,5%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>18,88%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>30,68%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>32788</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>24929</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>41765</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>32988</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>41144</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>22,66%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>28,87%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>43627</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33097</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>54804</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>76415</t>
+          <t>72165</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64027</t>
+          <t>60323</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91180</t>
+          <t>85892</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8626</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15051</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5375</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2931</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10144</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5487</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2504</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>10566</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>2242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12029</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>144685</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>144685</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>144685</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>145593</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>145593</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>145593</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>325824</t>
+          <t>312279</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>325824</t>
+          <t>312279</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>325824</t>
+          <t>312279</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>112666</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>95658</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>130745</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>120579</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>101031</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>139218</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>18,61%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>21,49%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>115285</t>
+          <t>126118</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98810</t>
+          <t>110347</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>134867</t>
+          <t>145085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>235864</t>
+          <t>238784</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>211942</t>
+          <t>214646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>267237</t>
+          <t>265405</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>344463</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>319036</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>371426</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>50,43%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>54,38%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>307476</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>264486</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>333685</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>47,47%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>51,51%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>365120</t>
+          <t>304159</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337665</t>
+          <t>284684</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395340</t>
+          <t>326541</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>672595</t>
+          <t>648622</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>622474</t>
+          <t>617018</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>712207</t>
+          <t>687015</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>166597</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>146588</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>189356</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>172131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>144856</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>240994</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>22,36%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>37,2%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>189597</t>
+          <t>145143</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>165196</t>
+          <t>127863</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>217037</t>
+          <t>163246</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>361728</t>
+          <t>311740</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>325581</t>
+          <t>283320</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>429557</t>
+          <t>341702</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>37035</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>28583</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>48799</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>24669</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>16076</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>47196</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>7,29%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>25680</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>67956</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91716</t>
+          <t>68979</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>22227</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>15446</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>30452</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>22927</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>16564</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>32459</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>28160</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>42736</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37748</t>
+          <t>33687</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>53726</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>907</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>647782</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>647782</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>647782</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614080</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614080</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614080</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1387335</t>
+          <t>1297068</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1387335</t>
+          <t>1297068</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1387335</t>
+          <t>1297068</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
